--- a/FILES/VENTE_PAR_CATEGORIE/category-sales-summary-2026-10-08-2026-10-08.xlsx
+++ b/FILES/VENTE_PAR_CATEGORIE/category-sales-summary-2026-10-08-2026-10-08.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FANOMEZANA\SUIVI SERVICE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FANOMEZANA\PROJETS\NOUVEAUX_RECAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18D32834-0A34-46AD-BAD2-71BAA2F49273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6BE5CD7-77FA-4EE5-8692-5858B9CC639C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{4B0B619B-259F-41D2-B6B4-65EF261BA29E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{CADE5226-B2F6-4B7D-97C4-E7F2FCDE88F2}"/>
   </bookViews>
   <sheets>
     <sheet name="category-sales-summary-2026-10-" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
     <t>FILTRE</t>
   </si>
   <si>
-    <t>5.000</t>
+    <t>6.000</t>
   </si>
   <si>
     <t>0.000</t>
@@ -67,25 +67,25 @@
     <t>HUILE BIDON</t>
   </si>
   <si>
-    <t>16.000</t>
+    <t>14.000</t>
   </si>
   <si>
     <t>HUILE EN VRAC</t>
   </si>
   <si>
-    <t>38.500</t>
+    <t>50.250</t>
   </si>
   <si>
     <t>LAVAGE</t>
   </si>
   <si>
-    <t>47.000</t>
+    <t>58.000</t>
   </si>
   <si>
     <t>LAVEUR</t>
   </si>
   <si>
-    <t>36.000</t>
+    <t>44.000</t>
   </si>
   <si>
     <t>PARALLELISME &amp; CARROSSAGE</t>
@@ -97,13 +97,13 @@
     <t>VIDANGE</t>
   </si>
   <si>
-    <t>13.000</t>
+    <t>15.000</t>
   </si>
   <si>
     <t>VULCA</t>
   </si>
   <si>
-    <t>7.000</t>
+    <t>46.000</t>
   </si>
 </sst>
 </file>
@@ -964,7 +964,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B94C655-26FB-4C0F-AFDF-838FE4871796}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D78FB2-5817-4B58-8350-9243ADFADA80}">
   <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1011,7 +1011,7 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>107000</v>
+        <v>147000</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
@@ -1023,13 +1023,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>107000</v>
+        <v>147000</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>107000</v>
+        <v>147000</v>
       </c>
       <c r="J2" s="1">
         <v>1</v>
@@ -1046,7 +1046,7 @@
         <v>15</v>
       </c>
       <c r="C3">
-        <v>1472000</v>
+        <v>992000</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -1058,16 +1058,16 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>1472000</v>
+        <v>992000</v>
       </c>
       <c r="H3">
         <v>838153</v>
       </c>
       <c r="I3">
-        <v>633847</v>
+        <v>153847</v>
       </c>
       <c r="J3" s="1">
-        <v>0.43</v>
+        <v>0.15</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>17</v>
       </c>
       <c r="C4">
-        <v>1019000</v>
+        <v>1329000</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -1093,13 +1093,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>1019000</v>
+        <v>1329000</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>1019000</v>
+        <v>1329000</v>
       </c>
       <c r="J4" s="1">
         <v>1</v>
@@ -1116,7 +1116,7 @@
         <v>19</v>
       </c>
       <c r="C5">
-        <v>342000</v>
+        <v>427000</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
@@ -1128,13 +1128,13 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>342000</v>
+        <v>427000</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>342000</v>
+        <v>427000</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
@@ -1221,7 +1221,7 @@
         <v>25</v>
       </c>
       <c r="C8">
-        <v>110000</v>
+        <v>135000</v>
       </c>
       <c r="D8" t="s">
         <v>13</v>
@@ -1233,13 +1233,13 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>110000</v>
+        <v>135000</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>110000</v>
+        <v>135000</v>
       </c>
       <c r="J8" s="1">
         <v>1</v>
@@ -1256,7 +1256,7 @@
         <v>27</v>
       </c>
       <c r="C9">
-        <v>23000</v>
+        <v>63000</v>
       </c>
       <c r="D9" t="s">
         <v>13</v>
@@ -1268,13 +1268,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>23000</v>
+        <v>63000</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>23000</v>
+        <v>63000</v>
       </c>
       <c r="J9" s="1">
         <v>1</v>
